--- a/templates/Day Mess Menu.template.xlsx
+++ b/templates/Day Mess Menu.template.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -560,6 +560,61 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Meal</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Timings</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>8 AM to 10 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -571,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -716,6 +771,61 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Meal</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Timings</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>8 AM to 10 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -727,7 +837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -857,6 +967,61 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Meal</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Timings</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>8 AM to 10 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -868,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -998,6 +1163,61 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Meal</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Timings</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>8 AM to 10 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
